--- a/testdata/testdata_input.xlsx
+++ b/testdata/testdata_input.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\PycharmProjects\automation-excercise-playwright-py\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957C131C-017C-4C42-8A33-BEC7974EDC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7135D2A6-D6E0-4CBB-9973-899A3AEE1462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="input_data" sheetId="1" r:id="rId1"/>
+    <sheet name="end_to_end" sheetId="1" r:id="rId1"/>
     <sheet name="registration" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>testcase_id</t>
   </si>
@@ -92,15 +92,6 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>fullname</t>
-  </si>
-  <si>
-    <t>Elizabeth Greene</t>
-  </si>
-  <si>
-    <t>kmcknight@example.net</t>
-  </si>
-  <si>
     <t>Registration</t>
   </si>
   <si>
@@ -114,6 +105,12 @@
   </si>
   <si>
     <t>Peterson</t>
+  </si>
+  <si>
+    <t>ScottSalinas370@tester.com</t>
+  </si>
+  <si>
+    <t>Salinas</t>
   </si>
 </sst>
 </file>
@@ -154,7 +151,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,6 +161,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -181,13 +184,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -503,41 +507,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{D9C5FE9F-95A6-4A9E-9D01-E8B86F8FB28C}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{D3091A84-F81F-42F3-A30E-CA58549CE0C2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -623,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
@@ -645,16 +660,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>18</v>

--- a/testdata/testdata_input.xlsx
+++ b/testdata/testdata_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\PycharmProjects\automation-excercise-playwright-py\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7135D2A6-D6E0-4CBB-9973-899A3AEE1462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24F732F-3F3A-4D74-82B7-48C646FC357C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>testcase_id</t>
   </si>
@@ -111,6 +111,39 @@
   </si>
   <si>
     <t>Salinas</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>T Shirt</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>for testing purposes</t>
+  </si>
+  <si>
+    <t>cc_name</t>
+  </si>
+  <si>
+    <t>cc_number</t>
+  </si>
+  <si>
+    <t>cc_cvv</t>
+  </si>
+  <si>
+    <t>cc_exp_month</t>
+  </si>
+  <si>
+    <t>cc_exp_year</t>
+  </si>
+  <si>
+    <t>Payor</t>
+  </si>
+  <si>
+    <t>5111-1111-1111-1118</t>
   </si>
 </sst>
 </file>
@@ -507,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -515,9 +548,16 @@
     <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,8 +573,29 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -546,6 +607,27 @@
       </c>
       <c r="E2" s="4" t="s">
         <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2">
+        <v>123</v>
+      </c>
+      <c r="K2">
+        <v>12</v>
+      </c>
+      <c r="L2">
+        <v>2035</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/testdata_input.xlsx
+++ b/testdata/testdata_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\PycharmProjects\automation-excercise-playwright-py\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24F732F-3F3A-4D74-82B7-48C646FC357C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE3C984-7C6D-4E35-9866-680A9977F534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
   <si>
     <t>testcase_id</t>
   </si>
@@ -144,6 +144,48 @@
   </si>
   <si>
     <t>5111-1111-1111-1118</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>men</t>
+  </si>
+  <si>
+    <t>women</t>
+  </si>
+  <si>
+    <t>tshirts</t>
+  </si>
+  <si>
+    <t>dress</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>Buy T-Shirt by Searching The Product</t>
+  </si>
+  <si>
+    <t>Buy Women Dress from Category</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>search product</t>
+  </si>
+  <si>
+    <t>product category</t>
+  </si>
+  <si>
+    <t>subcategory</t>
   </si>
 </sst>
 </file>
@@ -153,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +221,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -540,24 +588,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,31 +626,46 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
       <c r="C2" t="s">
         <v>29</v>
       </c>
@@ -609,31 +676,110 @@
         <v>18</v>
       </c>
       <c r="F2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" t="s">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" t="s">
         <v>33</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>39</v>
       </c>
-      <c r="I2" t="s">
+      <c r="M2" t="s">
         <v>40</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>123</v>
       </c>
-      <c r="K2">
+      <c r="O2">
         <v>12</v>
       </c>
-      <c r="L2">
+      <c r="P2">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3">
+        <v>123</v>
+      </c>
+      <c r="O3">
+        <v>12</v>
+      </c>
+      <c r="P3">
         <v>2035</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H3" xr:uid="{673DF045-3FEC-477C-BD08-8788BC19F378}">
+      <formula1>"women, men, kids"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I3" xr:uid="{FA2F32D7-00E1-4FD6-BF06-92DB13E06098}">
+      <formula1>"dress, tops, saree, tshirts, jeans"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3" xr:uid="{5FFD32CA-FCB6-443C-86DF-61FBD304F032}">
+      <formula1>"NA, polo, h&amp;m, madame, mast harbour, babyhug, allen solly junior, kookie, biba"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3" xr:uid="{98FDA8CB-F717-4AD0-A9B2-8F67DDCB697A}">
+      <formula1>"search product, product category, product brand"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{D9C5FE9F-95A6-4A9E-9D01-E8B86F8FB28C}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{D3091A84-F81F-42F3-A30E-CA58549CE0C2}"/>
+    <hyperlink ref="E3" r:id="rId3" xr:uid="{E24390BB-4BC0-46C8-87E4-D9553504DB62}"/>
+    <hyperlink ref="D3" r:id="rId4" xr:uid="{93B4BC8E-D8EF-41B4-BC18-1A10266EF562}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/testdata/testdata_input.xlsx
+++ b/testdata/testdata_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\PycharmProjects\automation-excercise-playwright-py\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE3C984-7C6D-4E35-9866-680A9977F534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14BEF52-F3BF-423E-9338-CC57314395F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
   <si>
     <t>testcase_id</t>
   </si>
@@ -186,6 +186,18 @@
   </si>
   <si>
     <t>subcategory</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>Buy Branded Clothes</t>
+  </si>
+  <si>
+    <t>product brand</t>
+  </si>
+  <si>
+    <t>polo</t>
   </si>
 </sst>
 </file>
@@ -588,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -759,19 +771,69 @@
         <v>2035</v>
       </c>
     </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4">
+        <v>123</v>
+      </c>
+      <c r="O4">
+        <v>12</v>
+      </c>
+      <c r="P4">
+        <v>2035</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H3" xr:uid="{673DF045-3FEC-477C-BD08-8788BC19F378}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H4" xr:uid="{673DF045-3FEC-477C-BD08-8788BC19F378}">
       <formula1>"women, men, kids"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I3" xr:uid="{FA2F32D7-00E1-4FD6-BF06-92DB13E06098}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4" xr:uid="{FA2F32D7-00E1-4FD6-BF06-92DB13E06098}">
       <formula1>"dress, tops, saree, tshirts, jeans"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3" xr:uid="{5FFD32CA-FCB6-443C-86DF-61FBD304F032}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4" xr:uid="{5FFD32CA-FCB6-443C-86DF-61FBD304F032}">
       <formula1>"NA, polo, h&amp;m, madame, mast harbour, babyhug, allen solly junior, kookie, biba"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3" xr:uid="{98FDA8CB-F717-4AD0-A9B2-8F67DDCB697A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{98FDA8CB-F717-4AD0-A9B2-8F67DDCB697A}">
       <formula1>"search product, product category, product brand"</formula1>
     </dataValidation>
   </dataValidations>
@@ -780,6 +842,8 @@
     <hyperlink ref="D2" r:id="rId2" xr:uid="{D3091A84-F81F-42F3-A30E-CA58549CE0C2}"/>
     <hyperlink ref="E3" r:id="rId3" xr:uid="{E24390BB-4BC0-46C8-87E4-D9553504DB62}"/>
     <hyperlink ref="D3" r:id="rId4" xr:uid="{93B4BC8E-D8EF-41B4-BC18-1A10266EF562}"/>
+    <hyperlink ref="E4" r:id="rId5" xr:uid="{B36CDD7B-4BA9-447B-BB8E-E6D4857B2C44}"/>
+    <hyperlink ref="D4" r:id="rId6" xr:uid="{F7D9AA2A-0472-430B-AFB1-5757BF5377CA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/testdata/testdata_input.xlsx
+++ b/testdata/testdata_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\PycharmProjects\automation-excercise-playwright-py\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14BEF52-F3BF-423E-9338-CC57314395F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EE4007-9B09-4D0D-BF9D-E23B58B6E5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
   <si>
     <t>testcase_id</t>
   </si>
@@ -149,9 +149,6 @@
     <t>category</t>
   </si>
   <si>
-    <t>men</t>
-  </si>
-  <si>
     <t>women</t>
   </si>
   <si>
@@ -198,6 +195,24 @@
   </si>
   <si>
     <t>polo</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>Remove Product from chart</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>remove</t>
+  </si>
+  <si>
+    <t>cart</t>
+  </si>
+  <si>
+    <t>Kids</t>
   </si>
 </sst>
 </file>
@@ -600,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -609,19 +624,20 @@
     <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,45 +654,48 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
@@ -688,45 +707,48 @@
         <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
-        <v>42</v>
-      </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" t="s">
         <v>33</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>40</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>123</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>12</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
@@ -738,45 +760,48 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" t="s">
         <v>49</v>
       </c>
-      <c r="H3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>33</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>39</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>40</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>123</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>12</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>2035</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
       </c>
       <c r="C4" t="s">
         <v>29</v>
@@ -788,53 +813,112 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" t="s">
         <v>57</v>
       </c>
-      <c r="G4" t="s">
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4">
+        <v>123</v>
+      </c>
+      <c r="P4">
+        <v>12</v>
+      </c>
+      <c r="Q4">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" t="s">
         <v>49</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J5" t="s">
         <v>43</v>
       </c>
-      <c r="I4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="K5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" t="s">
         <v>33</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M5" t="s">
         <v>39</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N5" t="s">
         <v>40</v>
       </c>
-      <c r="N4">
+      <c r="O5">
         <v>123</v>
       </c>
-      <c r="O4">
+      <c r="P5">
         <v>12</v>
       </c>
-      <c r="P4">
+      <c r="Q5">
         <v>2035</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H4" xr:uid="{673DF045-3FEC-477C-BD08-8788BC19F378}">
-      <formula1>"women, men, kids"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I4" xr:uid="{FA2F32D7-00E1-4FD6-BF06-92DB13E06098}">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J5" xr:uid="{FA2F32D7-00E1-4FD6-BF06-92DB13E06098}">
       <formula1>"dress, tops, saree, tshirts, jeans"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4" xr:uid="{5FFD32CA-FCB6-443C-86DF-61FBD304F032}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K5" xr:uid="{5FFD32CA-FCB6-443C-86DF-61FBD304F032}">
       <formula1>"NA, polo, h&amp;m, madame, mast harbour, babyhug, allen solly junior, kookie, biba"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{98FDA8CB-F717-4AD0-A9B2-8F67DDCB697A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F5" xr:uid="{98FDA8CB-F717-4AD0-A9B2-8F67DDCB697A}">
       <formula1>"search product, product category, product brand"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I5" xr:uid="{34B228A0-D262-48DE-942A-4939AA1F046E}">
+      <formula1>"women, men, kids, NA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G5" xr:uid="{27CDEE94-4B94-4778-A2B2-7AA3896892B3}">
+      <formula1>"add, remove"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -844,6 +928,8 @@
     <hyperlink ref="D3" r:id="rId4" xr:uid="{93B4BC8E-D8EF-41B4-BC18-1A10266EF562}"/>
     <hyperlink ref="E4" r:id="rId5" xr:uid="{B36CDD7B-4BA9-447B-BB8E-E6D4857B2C44}"/>
     <hyperlink ref="D4" r:id="rId6" xr:uid="{F7D9AA2A-0472-430B-AFB1-5757BF5377CA}"/>
+    <hyperlink ref="E5" r:id="rId7" xr:uid="{FC9B177A-9803-41FD-A937-4AAD244AE7CA}"/>
+    <hyperlink ref="D5" r:id="rId8" xr:uid="{01E47BD5-5E6F-48E5-B0C5-890BD28E9D00}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/testdata/testdata_input.xlsx
+++ b/testdata/testdata_input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\PycharmProjects\automation-excercise-playwright-py\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EE4007-9B09-4D0D-BF9D-E23B58B6E5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2512A5B0-8401-4339-A7C0-62AEBB13208C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,12 +101,6 @@
     <t>Delete Account</t>
   </si>
   <si>
-    <t>PatrickPeterson565@tester.com</t>
-  </si>
-  <si>
-    <t>Peterson</t>
-  </si>
-  <si>
     <t>ScottSalinas370@tester.com</t>
   </si>
   <si>
@@ -213,6 +207,12 @@
   </si>
   <si>
     <t>Kids</t>
+  </si>
+  <si>
+    <t>Powell</t>
+  </si>
+  <si>
+    <t>ZacharyPowell770@tester.com</t>
   </si>
 </sst>
 </file>
@@ -654,40 +654,40 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -695,43 +695,43 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O2">
         <v>123</v>
@@ -748,43 +748,43 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
         <v>42</v>
       </c>
-      <c r="J3" t="s">
-        <v>44</v>
-      </c>
       <c r="K3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O3">
         <v>123</v>
@@ -798,46 +798,46 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O4">
         <v>123</v>
@@ -851,46 +851,46 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" t="s">
         <v>61</v>
       </c>
-      <c r="H5" t="s">
-        <v>63</v>
-      </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O5">
         <v>123</v>
@@ -925,11 +925,9 @@
     <hyperlink ref="E2" r:id="rId1" xr:uid="{D9C5FE9F-95A6-4A9E-9D01-E8B86F8FB28C}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{D3091A84-F81F-42F3-A30E-CA58549CE0C2}"/>
     <hyperlink ref="E3" r:id="rId3" xr:uid="{E24390BB-4BC0-46C8-87E4-D9553504DB62}"/>
-    <hyperlink ref="D3" r:id="rId4" xr:uid="{93B4BC8E-D8EF-41B4-BC18-1A10266EF562}"/>
-    <hyperlink ref="E4" r:id="rId5" xr:uid="{B36CDD7B-4BA9-447B-BB8E-E6D4857B2C44}"/>
-    <hyperlink ref="D4" r:id="rId6" xr:uid="{F7D9AA2A-0472-430B-AFB1-5757BF5377CA}"/>
-    <hyperlink ref="E5" r:id="rId7" xr:uid="{FC9B177A-9803-41FD-A937-4AAD244AE7CA}"/>
-    <hyperlink ref="D5" r:id="rId8" xr:uid="{01E47BD5-5E6F-48E5-B0C5-890BD28E9D00}"/>
+    <hyperlink ref="E4" r:id="rId4" xr:uid="{B36CDD7B-4BA9-447B-BB8E-E6D4857B2C44}"/>
+    <hyperlink ref="E5" r:id="rId5" xr:uid="{FC9B177A-9803-41FD-A937-4AAD244AE7CA}"/>
+    <hyperlink ref="D3:D5" r:id="rId6" display="ZacharyPowell770@tester.com" xr:uid="{4B91064E-7B57-4E19-A5E6-8FF57984C2D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1070,8 +1068,8 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{0786DD06-0FF6-49EE-9163-0579E65E4030}"/>
-    <hyperlink ref="E3" r:id="rId3" xr:uid="{EB74EDB3-05A6-4495-8ED6-4651A1FD5B8F}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{EB74EDB3-05A6-4495-8ED6-4651A1FD5B8F}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{EE56746A-212B-4732-8401-A7B1654294BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
